--- a/results/job_matches_2026-09-03.xlsx
+++ b/results/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator</t>
+          <t>^Data Engineer - 6461115</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,207 +496,207 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a74613dbe565650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Richmond</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
+          <t>https://www.indeed.com/viewjob?jk=d327cf6aabca3bf4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e7624bacd3c7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=97c9639c442911cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83656a632b29e691</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5bcfb63295905b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8cba22bfa4507f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f700b926bc75474</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Enterprise Applications Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Beta Bionics, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, SQS, SNS, API Gateway, ECS</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a36044a8c65468</t>
+          <t>https://www.indeed.com/viewjob?jk=2e249f1007751107</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>System Engineer – Site Reliability Engineering (SRE)</t>
+          <t>Sr. Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, Redshift, S3, SQS, RDS, Azure, Databricks, Event Hubs, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
+          <t>https://www.indeed.com/viewjob?jk=279b005ffce20271</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>MLOps &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sierra Nevada Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lone Tree, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e48bddbab8709</t>
+          <t>https://www.indeed.com/viewjob?jk=8d119b132aefd5a1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Databricks Administrator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb849225e8b2c49</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Richmond</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
+          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Application Engineer</t>
+          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ba8fa97901475</t>
+          <t>https://www.indeed.com/viewjob?jk=74e7624bacd3c7f1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer</t>
+          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=83656a632b29e691</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer Technology</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,89 +916,89 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8cba22bfa4507f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Enterprise Applications Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Beta Bionics, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, SQS, SNS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
+          <t>https://www.indeed.com/viewjob?jk=55a36044a8c65468</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>System Engineer – Site Reliability Engineering (SRE)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e48bddbab8709</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80690607da1933cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb849225e8b2c49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Sr. Software Application Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ba8fa97901475</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Full Stack Product Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
+          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
+          <t>AWS DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
+          <t>https://www.indeed.com/viewjob?jk=d29dcd9067394b82</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Software Engineer III - Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
+          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer Technology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Artificial Intelligence / Machine Learning Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
+          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
+          <t>https://www.indeed.com/viewjob?jk=80690607da1933cc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Production Support Engineering PMTS</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
+          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solutions Architect, Forward Deployed</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, RDS, Azure, Databricks, Vertex AI, Snowflake</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9f571d1cebb697</t>
+          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510b1e334c4fe4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,85 +1493,85 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf704911ff39cc0e</t>
+          <t>https://www.indeed.com/viewjob?jk=94e187ddd5c7b1c5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c14c404355ce78</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TripleLift</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
+          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence / Machine Learning Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
+          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
+          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (AWS)</t>
+          <t>Solutions Architect, Forward Deployed</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, RDS, Azure, Databricks, Vertex AI, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9f571d1cebb697</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Analytics</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
+          <t>https://www.indeed.com/viewjob?jk=510b1e334c4fe4f9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gravie</t>
+          <t>TripleLift</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Dataflow, Scala, NoSQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4285c04ca20cf636</t>
+          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>Specialist, Technology Engineer (AWS)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer (Knowledge Graph)</t>
+          <t>Software Engineer - Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Gravie</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Dataflow, Scala, NoSQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
+          <t>https://www.indeed.com/viewjob?jk=4285c04ca20cf636</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
+          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
+          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Databricks Administration Specialist</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
+          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer III</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,137 +2316,137 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
+          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa2c8c48e2498cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,49 +2491,49 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Software Engineer I, Enterprise Financial Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
+          <t>https://www.indeed.com/viewjob?jk=916917e5abcd591e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Backend Developer – Python</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2547,11 +2547,11 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fb8147abac9706</t>
+          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tester Senior</t>
+          <t>Business Intelligence Developer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
+          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer Senior - Mortgage Platforms</t>
+          <t>Databricks Administration Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
+          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer-Intermediate Level</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Techtronic Industries Co. Ltd</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa2c8c48e2498cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
+          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
+          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior SDET - Architect</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Attain</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, Dask, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bc14828ef1e67f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
+          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
+          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SCOR</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,102 +3016,102 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Data Engineer/Data Scientist</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
+          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Development Engineer</t>
+          <t>Senior SDET - Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c4d5515734cd07</t>
+          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Tester Senior</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38b2d7dd112b433</t>
+          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
+          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GXO Logistics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>First Onsite</t>
+          <t>SCOR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,137 +3261,137 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
+          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
+          <t>Software Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
+          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Storage Platform Engineer</t>
+          <t>AI-Enabled Data Architecture Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Bannockburn, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer(Distributed Systems)</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
+          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
+          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Digital Platform Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Comtek Intl</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e5b707656920a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer - Reliability</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,102 +3716,102 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
+          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer Full stack</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
+          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
+          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Database Developer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Herschend Family Entertainment</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,42 +3821,1617 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
+          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NoSQL Database Engineer || Onsite</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ukund</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer-Marketplace</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Staples</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Framingham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI Product Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BDIPlus</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GXO Logistics</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>First Onsite</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Greenwood Village, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
         <v>10.4</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, GCP, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9314bc9cfb51fe1b</t>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Burlington Stores</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Edgewater Park, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Storage Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Pacific Gas and Electric</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TBC Corporation</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Development Engineer(Distributed Systems)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Akron, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Databricks Data Engineer - Reliability</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Scientific Games</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Engineer Full stack</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Sr. Database Developer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Herschend Family Entertainment</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Peachtree Corners, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Techtronic Industries Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DevOps Engineer – Azure Platform</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a738da303dc8ffd2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-03.xlsx
+++ b/results/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator</t>
+          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Richmond</t>
+          <t>Senior Databricks Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
+          <t>Managing Consultant, Databricks Engineer - Richmond</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e7624bacd3c7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83656a632b29e691</t>
+          <t>https://www.indeed.com/viewjob?jk=74e7624bacd3c7f1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8cba22bfa4507f</t>
+          <t>https://www.indeed.com/viewjob?jk=83656a632b29e691</t>
         </is>
       </c>
     </row>
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>System Engineer – Site Reliability Engineering (SRE)</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8cba22bfa4507f</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb849225e8b2c49</t>
+          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>System Engineer – Site Reliability Engineering (SRE)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Application Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ba8fa97901475</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb849225e8b2c49</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer Technology</t>
+          <t>Software Engineer III - Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer Technology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=80690607da1933cc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80690607da1933cc</t>
+          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
+          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
+          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TripleLift</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
+          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>TripleLift</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (AWS)</t>
+          <t>Software Engineer - Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
+          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Analytics</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
+          <t>S3, RDS, Hadoop, HDFS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
+          <t>https://www.indeed.com/viewjob?jk=3cfaf25e543ddfa3</t>
         </is>
       </c>
     </row>
@@ -2008,25 +2008,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Dataflow, Scala, NoSQL, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4285c04ca20cf636</t>
+          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
+          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
+          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer I, Enterprise Financial Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
+          <t>https://www.indeed.com/viewjob?jk=916917e5abcd591e</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer I, Enterprise Financial Technology</t>
+          <t>Business Intelligence Developer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=916917e5abcd591e</t>
+          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer III</t>
+          <t>Databricks Administration Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
+          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Administration Specialist</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa2c8c48e2498cf</t>
+          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
+          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Contractor -Alteryx Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
+          <t>https://www.indeed.com/viewjob?jk=8230de67e8440ae5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
+          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
+          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
+          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
+          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior SDET - Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior SDET - Architect</t>
+          <t>Tester Senior</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tester Senior</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
+          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SCOR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer</t>
+          <t>Software Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SCOR</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
+          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Data Engineer/Data Scientist</t>
+          <t>Senior Software Engineer-Marketplace</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
+          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
+          <t>AI-Enabled Data Architecture Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Bannockburn, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI-Enabled Data Architecture Consultant</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bannockburn, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
+          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
+          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
+          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
+          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
+          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
+          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
+          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
+          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
+          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
+          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
+          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
+          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
+          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
+          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
+          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
+          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
+          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
+          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Marketplace</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>GXO Logistics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,67 +4766,67 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
+          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Development Engineer(Distributed Systems)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GXO Logistics</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>First Onsite</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
+          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>First Onsite</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
+          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Storage Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Development Engineer(Distributed Systems)</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
+          <t>https://www.indeed.com/viewjob?jk=acae8b3a9f218a11</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>CESO, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Akron, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
+          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
+          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
+          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
+          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer - Reliability</t>
+          <t>Software Engineer Full stack</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer Full stack</t>
+          <t>Sr. Database Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Herschend Family Entertainment</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
+          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Techtronic Industries Co. Ltd</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
+          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Database Developer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Herschend Family Entertainment</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5360,76 +5360,6 @@
         </is>
       </c>
       <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Techtronic Industries Co. Ltd</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Azure Platform</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a738da303dc8ffd2</t>
         </is>

--- a/results/job_matches_2026-09-03.xlsx
+++ b/results/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLOps &amp; Data Engineer</t>
+          <t>Data Engineer Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sierra Nevada Corporation</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lone Tree, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d119b132aefd5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
+          <t>MLOps &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Sierra Nevada Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lone Tree, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
+          <t>https://www.indeed.com/viewjob?jk=8d119b132aefd5a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator</t>
+          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,52 +801,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Richmond</t>
+          <t>Senior Databricks Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>System Engineer – Site Reliability Engineering (SRE)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e48bddbab8709</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e48bddbab8709</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>System Engineer – Site Reliability Engineering (SRE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Product Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb849225e8b2c49</t>
+          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer</t>
+          <t>AWS DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=d29dcd9067394b82</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer (Hybrid)</t>
+          <t>Software Engineer III - Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29dcd9067394b82</t>
+          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer Technology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Team Center PLM Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf50044bf3b2178</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
+          <t>Artificial Intelligence / Machine Learning Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
+          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Artificial Intelligence / Machine Learning Developer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
+          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
+          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
+          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>TripleLift</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer - Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TripleLift</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Analytics</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S3, RDS, Hadoop, HDFS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cfaf25e543ddfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gravie</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
+          <t>S3, RDS, Hadoop, HDFS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
+          <t>https://www.indeed.com/viewjob?jk=3cfaf25e543ddfa3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e38d53eb67f89550</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Computing Engineer/Software Developer –AI/ML, GUI Development, Custom Cobot Control</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Custom Manufacturing and Engineering</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pinellas Park, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, PostgreSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
+          <t>https://www.indeed.com/viewjob?jk=e97b8b145647f2bc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Gravie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
+          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
+          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
+          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
+          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer I, Enterprise Financial Technology</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=916917e5abcd591e</t>
+          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
+          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer III</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Databricks Administration Specialist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Databricks Administration Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Business Intelligence Developer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
+          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
+          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
+          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Contractor -Alteryx Developer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8230de67e8440ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
+          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
+          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
+          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior SDET - Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tester Senior</t>
+          <t>Senior SDET - Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
+          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Tester Senior</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
+          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SCOR</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Data Engineer/Data Scientist</t>
+          <t>Senior Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SCOR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
+          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Marketplace</t>
+          <t>AI-Enabled Data Architecture Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Bannockburn, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI-Enabled Data Architecture Consultant</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bannockburn, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
+          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
+          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
+          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
+          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
+          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
+          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
+          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
+          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
+          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
+          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
+          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
+          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
+          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
+          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
+          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
+          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
+          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
+          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Software Engineer-Marketplace</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
         </is>
       </c>
     </row>
@@ -4773,17 +4773,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Development Engineer(Distributed Systems)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>First Onsite</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>First Onsite</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
+          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer(Distributed Systems)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Storage Platform Engineer</t>
+          <t>.Net developer (strong Azure)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Stier Solutions Inc</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
         </is>
       </c>
     </row>
@@ -5228,17 +5228,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer Full stack</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Techtronic Industries Co. Ltd</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
+          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Database Developer</t>
+          <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Herschend Family Entertainment</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5290,76 +5290,6 @@
         </is>
       </c>
       <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Techtronic Industries Co. Ltd</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Azure Platform</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a738da303dc8ffd2</t>
         </is>

--- a/results/job_matches_2026-09-03.xlsx
+++ b/results/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,47 +491,47 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a74613dbe565650</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6fe2dd4415dd8d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>^Data Engineer - 6461115</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, HDFS, Hive, Sqoop, Oozie, YARN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d327cf6aabca3bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=4a74613dbe565650</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c9639c442911cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d327cf6aabca3bf4</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5bcfb63295905b</t>
+          <t>https://www.indeed.com/viewjob?jk=97c9639c442911cd</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f700b926bc75474</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5bcfb63295905b</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e249f1007751107</t>
+          <t>https://www.indeed.com/viewjob?jk=8f700b926bc75474</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ELLKAY, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Elmwood Park, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, SQS, RDS, Azure, Databricks, Event Hubs, GCP</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279b005ffce20271</t>
+          <t>https://www.indeed.com/viewjob?jk=2e249f1007751107</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer Consultant</t>
+          <t>Sr. Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>ELLKAY, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Elmwood Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, Redshift, S3, SQS, RDS, Azure, Databricks, Event Hubs, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
+          <t>https://www.indeed.com/viewjob?jk=279b005ffce20271</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOps &amp; Data Engineer</t>
+          <t>Java Developer with AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sierra Nevada Corporation</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lone Tree, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Google Cloud Platform, Dataflow, HBase, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d119b132aefd5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
+          <t>MLOps &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Sierra Nevada Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lone Tree, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
+          <t>https://www.indeed.com/viewjob?jk=8d119b132aefd5a1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator</t>
+          <t>Data Engineer Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
+          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
+          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, Databricks, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e7624bacd3c7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
+          <t>Senior Databricks Administrator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83656a632b29e691</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf2cd00a78b92f1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Enterprise Applications Developer</t>
+          <t>Forward Deployed Data Engineer - Houston</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Beta Bionics, Inc.</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, SQS, SNS, API Gateway, ECS</t>
+          <t>AWS, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a36044a8c65468</t>
+          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,129 +986,129 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8cba22bfa4507f</t>
+          <t>https://www.indeed.com/viewjob?jk=74e7624bacd3c7f1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>System Engineer – Site Reliability Engineering (SRE)</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
+          <t>https://www.indeed.com/viewjob?jk=f362c9602042b5aa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e48bddbab8709</t>
+          <t>https://www.indeed.com/viewjob?jk=fb65efe8a988bc77</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Fabric Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
+          <t>https://www.indeed.com/viewjob?jk=60c4ffa6f4022338</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e48bddbab8709</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer (Hybrid)</t>
+          <t>System Engineer – Site Reliability Engineering (SRE)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d29dcd9067394b82</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Full Stack Product Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Technology</t>
+          <t>AWS DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d29dcd9067394b82</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=80690607da1933cc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80690607da1933cc</t>
+          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Dataflow, Spark, Kafka</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74016e8b1c1cf6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Team Center PLM Architect</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf50044bf3b2178</t>
+          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Team Center PLM Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e187ddd5c7b1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf50044bf3b2178</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c14c404355ce78</t>
+          <t>https://www.indeed.com/viewjob?jk=82b602f77b928622</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Artificial Intelligence / Machine Learning Developer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
+          <t>https://www.indeed.com/viewjob?jk=31a58bed0c2d1c26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
+          <t>https://www.indeed.com/viewjob?jk=69e381d6a5f4918a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,242 +1651,242 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
+          <t>https://www.indeed.com/viewjob?jk=2928f8de05a5880f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
+          <t>https://www.indeed.com/viewjob?jk=59c0167102920ff0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solutions Architect, Forward Deployed</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, RDS, Azure, Databricks, Vertex AI, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9f571d1cebb697</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd92748e7a09744</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510b1e334c4fe4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3e74cdf07bf5cc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TripleLift</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3891bf419843c06e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
+          <t>https://www.indeed.com/viewjob?jk=cfba9c82293ef7b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Analytics</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
+          <t>https://www.indeed.com/viewjob?jk=9554b027ea016221</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=151ab6f759331e5f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5e0807495bc5b0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
+          <t>https://www.indeed.com/viewjob?jk=425e768e43b69bff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S3, RDS, Hadoop, HDFS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cfaf25e543ddfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e293e334c27ed7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38d53eb67f89550</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e6b189059b3dd8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Computing Engineer/Software Developer –AI/ML, GUI Development, Custom Cobot Control</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Custom Manufacturing and Engineering</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pinellas Park, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Spark, Scala, PostgreSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97b8b145647f2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=94e187ddd5c7b1c5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gravie</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,81 +2092,81 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c14c404355ce78</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
+          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
+          <t>https://www.indeed.com/viewjob?jk=67e889fa62a0aa04</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
+          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Solutions Architect, Forward Deployed</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, RDS, Azure, Databricks, Vertex AI, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9f571d1cebb697</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
+          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
+          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
+          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,347 +2491,347 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Administration Specialist</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
+          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer III</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
+          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
+          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>TripleLift</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
+          <t>https://www.indeed.com/viewjob?jk=e38d53eb67f89550</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Gravie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,137 +2911,137 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior SDET - Architect</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tester Senior</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
+          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
+          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,84 +3226,84 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SCOR</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI-Enabled Data Architecture Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bannockburn, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
+          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,32 +3313,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,50 +3348,50 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Business Intelligence Developer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
+          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Databricks Administration Specialist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
+          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
+          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
+          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,102 +3681,102 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
+          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
+          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior SDET - Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
+          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Tester Senior</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Software Engineer (Data Backend)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
+          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>AI-Enabled Data Architecture Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bannockburn, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
+          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
+          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
+          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
+          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
+          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
+          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
+          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
+          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Marketplace</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GXO Logistics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
+          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>First Onsite</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
+          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Development Engineer(Distributed Systems)</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,102 +4976,102 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>.Net developer (strong Azure)</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Stier Solutions Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae8b3a9f218a11</t>
+          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
+          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
+          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,75 +5221,845 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
+          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
+          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Edgewater Federal Solutions</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2d71f3740aa0ae6</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer-Marketplace</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Staples</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Framingham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GXO Logistics</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Cloud Data Architect</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>TBC Corporation</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Development Engineer(Distributed Systems)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>University of Tennessee Health Science Center</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>University of Tennessee</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>In-N-Out Burger</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>First Onsite</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Greenwood Village, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>.Net developer (strong Azure)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Stier Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Java AWS Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acae8b3a9f218a11</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sherwin-Williams</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Akron, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>DevOps Engineer – Azure Platform</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>UniFirst</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Wilmington, MA, US USA</t>
         </is>
       </c>
-      <c r="D139" t="n">
+      <c r="D161" t="n">
         <v>10.4</v>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a738da303dc8ffd2</t>
         </is>

--- a/results/job_matches_2026-09-03.xlsx
+++ b/results/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>System Engineer – Site Reliability Engineering (SRE)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
+          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer</t>
+          <t>System Engineer – Site Reliability Engineering (SRE)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, HBase, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Team Center PLM Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf50044bf3b2178</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Integration Engineer II</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
+          <t>https://www.indeed.com/viewjob?jk=59c0167102920ff0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Team Center PLM Architect</t>
+          <t>Senior SQL Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf50044bf3b2178</t>
+          <t>https://www.indeed.com/viewjob?jk=82b602f77b928622</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b602f77b928622</t>
+          <t>https://www.indeed.com/viewjob?jk=31a58bed0c2d1c26</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31a58bed0c2d1c26</t>
+          <t>https://www.indeed.com/viewjob?jk=69e381d6a5f4918a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e381d6a5f4918a</t>
+          <t>https://www.indeed.com/viewjob?jk=2928f8de05a5880f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2928f8de05a5880f</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd92748e7a09744</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59c0167102920ff0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3e74cdf07bf5cc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd92748e7a09744</t>
+          <t>https://www.indeed.com/viewjob?jk=3891bf419843c06e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3e74cdf07bf5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cfba9c82293ef7b5</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3891bf419843c06e</t>
+          <t>https://www.indeed.com/viewjob?jk=9554b027ea016221</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfba9c82293ef7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=151ab6f759331e5f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9554b027ea016221</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5e0807495bc5b0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151ab6f759331e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=425e768e43b69bff</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5e0807495bc5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e293e334c27ed7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=425e768e43b69bff</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e6b189059b3dd8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e293e334c27ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior SQL Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e6b189059b3dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=94e187ddd5c7b1c5</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e187ddd5c7b1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c14c404355ce78</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,15 +2088,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c14c404355ce78</t>
+          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Sr. Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, RDS, Scala, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e889fa62a0aa04</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2e85c21a66a6ee</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
+          <t>https://www.indeed.com/viewjob?jk=67e889fa62a0aa04</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect, Forward Deployed</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, RDS, Azure, Databricks, Vertex AI, Snowflake</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9f571d1cebb697</t>
+          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect, Forward Deployed</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Rackspace Technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, RDS, Azure, Databricks, Vertex AI, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9f571d1cebb697</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Data Engineer – Customer AI Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
+          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
+          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
+          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
+          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
+          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TripleLift</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
+          <t>AWS, RDS, BigQuery, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>TripleLift</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38d53eb67f89550</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gravie</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
+          <t>https://www.indeed.com/viewjob?jk=e38d53eb67f89550</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Cyber Security Engineer - Automation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510c9bc96d1c2105</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd974acb38b1c48</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Developer - AI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
+          <t>https://www.indeed.com/viewjob?jk=16c7307c5a0e8d1d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, GCP, Vertex AI, Scala, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9e283de70978e9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer III</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
+          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Databricks Administration Specialist</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Business Intelligence Developer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Oracle, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c15960af921ffca8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Databricks, Spark, Scala, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
+          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
+          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>IT AI Senior Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Dataflow, Spark, PySpark, Scala, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e627602adc28fa2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior SDET - Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Ncontracts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tester Senior</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,77 +3881,77 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
+          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cyber Security Engineer - Automation</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
+          <t>https://www.indeed.com/viewjob?jk=0bdadf15bcddb227</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Backend)</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>JobSiteCare</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=53647361cafcb4a7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI-Enabled Data Architecture Consultant</t>
+          <t>Tester Senior</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bannockburn, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
+          <t>https://www.indeed.com/viewjob?jk=b76a6c5df30df079</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Software Engineer (Data Backend)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e731143bb29b7e3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Software Engineer - ITSM Service Now Team</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5eb0704509c08b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
+          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Java Developer - Enterprise Data (Hybrid)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Detroit Labs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, SQS, API Gateway, Scala, Kafka, Oracle, MySQL, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
+          <t>https://www.indeed.com/viewjob?jk=9a4cfadcb1467f03</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>AI-Enabled Data Architecture Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Bannockburn, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ELT, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
+          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
+          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
+          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
+          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
+          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
+          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Software Engineer-Marketplace</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,42 +4616,42 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,277 +4661,277 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
+          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=c559ad72b531e0fa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
+          <t>https://www.indeed.com/viewjob?jk=a455426ac5cd7dd2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CREDIT GENIE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7e0f7912d67eb7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Data Engineer - Paradox Machines</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Infinity</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
+          <t>https://www.indeed.com/viewjob?jk=4601fec51abe547d</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>IAM, RDS, Databricks, Spark, Kafka, Snowflake, Data Modeling, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Tennessee Health Science Center</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Tennessee</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,277 +4941,277 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
+          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
+          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, Scala, Kafka, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
+          <t>https://www.indeed.com/viewjob?jk=55cf49ee0837de3f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Context Layer Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>EMR, RDS, Databricks, Unity Catalog, Hadoop, Hive, MapReduce, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
+          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>.Net developer (strong Azure)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stier Solutions Inc</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
+          <t>https://www.indeed.com/viewjob?jk=acae8b3a9f218a11</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
+          <t>https://www.indeed.com/viewjob?jk=0704cc50203806f0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CESO, Inc.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Akron, OH, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CESO, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
+          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CESO, Inc.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
+          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Associate AI Solution Architect</t>
+          <t>Senior Full Stack Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,742 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Associate AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Edgewater Federal Solutions</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d71f3740aa0ae6</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer-Marketplace</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Staples</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Framingham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Event Hubs, HBase, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>GXO Logistics</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Cloud Data Architect</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>TBC Corporation</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Software Development Engineer(Distributed Systems)</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>University of Tennessee Health Science Center</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef7dc642e11018</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer: Office of Innovative Technologies - UTK</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>University of Tennessee</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Oracle, SQL Server, Data Modeling, Power BI</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f5baefea3d59e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>In-N-Out Burger</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30dda2e2ff7609b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>First Onsite</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Greenwood Village, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>.Net developer (strong Azure)</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Stier Solutions Inc</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f4d83b0093b2a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Java AWS Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acae8b3a9f218a11</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>SCADA Full Stack Application Developer - Industrial Automation</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Snowflake, Oracle, SQL Server, Tableau, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b704167109e006a</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>CESO, Inc.</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Akron, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>CESO, Inc.</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>CESO, Inc.</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, ELT, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Azure Platform</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a738da303dc8ffd2</t>
         </is>
       </c>
     </row>
